--- a/tests/fixtures/golden/corpus/report_spreadsheet.xlsx
+++ b/tests/fixtures/golden/corpus/report_spreadsheet.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -37,6 +37,10 @@
     </font>
     <font>
       <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <i val="1"/>
     </font>
   </fonts>
   <fills count="4">
@@ -69,7 +73,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -79,6 +83,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -153,6 +158,146 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="10"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Q4 2025 Revenue by Product Line ($000)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Revenue Analysis'!B15</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Revenue Analysis'!$A$16:$A$18</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Revenue Analysis'!$B$16:$B$18</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Product Line</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Revenue ($000)</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>13</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="3600000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -620,7 +765,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="80" customWidth="1" min="1" max="1"/>
@@ -845,8 +990,58 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>Chart Data (numeric $000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Product Line</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Q4 Total ($000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Widget</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>6340</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Gadget</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>3600</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>2460</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
